--- a/JetfWeb/JETFTAX/Download/貨件入庫批量上傳_範例.xlsx
+++ b/JetfWeb/JETFTAX/Download/貨件入庫批量上傳_範例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TFS\Thus\JETFTAX\JETFTAX\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Source\Jetf\JetfWeb\JETFTAX\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589624EA-B18D-4A08-9124-2CBEC75D8708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8585E946-EE05-4228-9034-53BBC2C7B683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>入庫日期</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -73,6 +82,10 @@
   </si>
   <si>
     <t>新竹退件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -80,7 +93,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -110,6 +123,14 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -136,17 +157,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -464,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC5097E-EBA7-4381-AA76-5BDA81C215A8}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" customWidth="1"/>
@@ -499,12 +521,12 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>46056</v>
       </c>
       <c r="B2" t="s">
@@ -519,12 +541,15 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="G2">
-        <v>30</v>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/JetfWeb/JETFTAX/Download/貨件入庫批量上傳_範例.xlsx
+++ b/JetfWeb/JETFTAX/Download/貨件入庫批量上傳_範例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Source\Jetf\JetfWeb\JETFTAX\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8585E946-EE05-4228-9034-53BBC2C7B683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BF2372DD4202C5EB07A95CA653EBA15F322A3458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>入庫日期</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -87,6 +87,12 @@
   <si>
     <t>小</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -168,13 +174,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="1" xr:uid="{F390750B-0C2B-4BFF-8BED-86A6A2D2D990}"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -485,8 +491,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC5097E-EBA7-4381-AA76-5BDA81C215A8}">
-  <dimension ref="A1:H8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" customWidth="1"/>
@@ -497,9 +503,10 @@
     <col min="6" max="6" width="18.88671875" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,8 +531,11 @@
       <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46056</v>
       </c>
@@ -547,9 +557,15 @@
       <c r="H2" t="s">
         <v>12</v>
       </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
